--- a/Squelette Prjet.xlsx
+++ b/Squelette Prjet.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9632B1A7-8F8D-4AB2-947C-0F4833DFFA6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{06A35ECA-C5EA-4944-82BA-1B81068DFB83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9289B49A-2C63-4256-91AE-55ED75D7450E}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,15 +36,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="52">
+  <si>
+    <t>Quoi ?</t>
+  </si>
+  <si>
+    <t>Quelle page ?</t>
+  </si>
   <si>
     <t>Temps (en h)</t>
   </si>
   <si>
-    <t>Quelle page ?</t>
-  </si>
-  <si>
-    <t>Quoi ?</t>
+    <t>Semaines</t>
   </si>
   <si>
     <t>BDD</t>
@@ -62,7 +65,10 @@
     <t>Vérification Connexion</t>
   </si>
   <si>
-    <t>Connexion Back</t>
+    <t>Affichage menu gauche</t>
+  </si>
+  <si>
+    <t>Toutes pages</t>
   </si>
   <si>
     <t>Affichage Calendrier</t>
@@ -71,24 +77,21 @@
     <t>Calendrier</t>
   </si>
   <si>
-    <t>Toutes pages</t>
-  </si>
-  <si>
     <t>Fil d'Arianne</t>
   </si>
   <si>
+    <t>Affichage Ajout intervention</t>
+  </si>
+  <si>
     <t>Intervention Ajouter</t>
   </si>
   <si>
-    <t>Affichage Ajout intervention</t>
+    <t>Ajout Intervention JS</t>
   </si>
   <si>
     <t>Ajouter Intervention</t>
   </si>
   <si>
-    <t>Ajout Intervention JS</t>
-  </si>
-  <si>
     <t xml:space="preserve">BDD </t>
   </si>
   <si>
@@ -116,9 +119,6 @@
     <t>Back vérification</t>
   </si>
   <si>
-    <t>???</t>
-  </si>
-  <si>
     <t>Double Vérification suppression</t>
   </si>
   <si>
@@ -131,36 +131,36 @@
     <t>Filtre</t>
   </si>
   <si>
+    <t>Modules enseignés affichage + BDD</t>
+  </si>
+  <si>
     <t>Fiche enseignant</t>
   </si>
   <si>
-    <t>Modules enseignés affichage + BDD</t>
-  </si>
-  <si>
-    <t>Semaines</t>
+    <t xml:space="preserve">Affichage </t>
   </si>
   <si>
     <t>Fiche enseignant -général</t>
   </si>
   <si>
-    <t xml:space="preserve">Affichage </t>
-  </si>
-  <si>
     <t>Fiche enseignant -interventions</t>
   </si>
   <si>
     <t>Modules</t>
   </si>
   <si>
+    <t>Flèches qui affichent et chevrons (optionnel)</t>
+  </si>
+  <si>
     <t>Modules : Fiches</t>
   </si>
   <si>
+    <t>Affichage et interraction</t>
+  </si>
+  <si>
     <t>Modules : suppression</t>
   </si>
   <si>
-    <t>Affichage et interraction</t>
-  </si>
-  <si>
     <t>Types d'intervention</t>
   </si>
   <si>
@@ -182,13 +182,16 @@
     <t>Condition pagination</t>
   </si>
   <si>
-    <t>Affichage menu gauche</t>
-  </si>
-  <si>
     <t>Menu coloré fonction page</t>
   </si>
   <si>
-    <t>Flèches qui affichent et chevrons (optionnel)</t>
+    <t>/</t>
+  </si>
+  <si>
+    <t>Verification Connexion</t>
+  </si>
+  <si>
+    <t>Liste provenant de la BDD</t>
   </si>
 </sst>
 </file>
@@ -565,10 +568,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F394B27-5784-44B6-B67D-118FA3C814D2}">
-  <dimension ref="A1:D37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D41"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.28515625" customWidth="1"/>
+    <col min="1" max="1" width="41" customWidth="1"/>
     <col min="2" max="2" width="28.28515625" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" customWidth="1"/>
     <col min="4" max="4" width="13.28515625" customWidth="1"/>
@@ -576,24 +579,24 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>33</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -601,10 +604,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3">
         <v>0.75</v>
@@ -612,10 +615,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
         <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
       </c>
       <c r="C4">
         <v>1.5</v>
@@ -623,10 +626,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -634,10 +637,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -645,10 +648,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7">
         <v>0.25</v>
@@ -659,7 +662,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C8">
         <v>3</v>
@@ -670,7 +673,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -678,10 +681,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
         <v>17</v>
-      </c>
-      <c r="B10" t="s">
-        <v>15</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -689,10 +692,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11">
         <v>3</v>
@@ -700,10 +703,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12">
         <v>4</v>
@@ -711,10 +714,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13">
         <v>1.5</v>
@@ -722,10 +725,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" t="s">
         <v>24</v>
-      </c>
-      <c r="B14" t="s">
-        <v>23</v>
       </c>
       <c r="C14">
         <v>3</v>
@@ -733,13 +736,13 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="C15">
+        <v>2.5</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -755,7 +758,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B17" t="s">
         <v>29</v>
@@ -777,10 +780,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" t="s">
         <v>32</v>
-      </c>
-      <c r="B19" t="s">
-        <v>31</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -788,7 +791,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B20" t="s">
         <v>34</v>
@@ -799,7 +802,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B21" t="s">
         <v>34</v>
@@ -810,10 +813,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C22">
         <v>1.5</v>
@@ -821,10 +824,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C23">
         <v>3</v>
@@ -832,10 +835,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -843,10 +846,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="B25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C25">
         <v>2.5</v>
@@ -854,7 +857,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B26" t="s">
         <v>38</v>
@@ -865,7 +868,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B27" t="s">
         <v>38</v>
@@ -876,10 +879,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" t="s">
         <v>40</v>
-      </c>
-      <c r="B28" t="s">
-        <v>39</v>
       </c>
       <c r="C28">
         <v>2</v>
@@ -887,7 +890,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B29" t="s">
         <v>41</v>
@@ -920,7 +923,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B32" t="s">
         <v>43</v>
@@ -931,7 +934,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B33" t="s">
         <v>43</v>
@@ -942,7 +945,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B34" t="s">
         <v>44</v>
@@ -975,13 +978,57 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C37">
         <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>50</v>
+      </c>
+      <c r="B38" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>51</v>
+      </c>
+      <c r="B39" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>51</v>
+      </c>
+      <c r="B40" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>51</v>
+      </c>
+      <c r="B41" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -990,15 +1037,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100875CF4D41AB6D2409A5BA134E78B9E42" ma:contentTypeVersion="1" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="987d2375e1aa7e5b3c3d3a9f8dc9e90d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="a0308db3-8c21-4eba-bd28-4114843e291b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3eb3843b39730996179047a7e2a43d60" ns3:_="">
     <xsd:import namespace="a0308db3-8c21-4eba-bd28-4114843e291b"/>
@@ -1124,6 +1162,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -1131,14 +1178,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67767696-35D8-426B-A51D-A65032437CBC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0726B72-C296-41E3-AEB8-64C259EDC63E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1156,17 +1195,25 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67767696-35D8-426B-A51D-A65032437CBC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88D1B06E-3D00-4009-8FCB-176A42714ECA}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="a0308db3-8c21-4eba-bd28-4114843e291b"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="a0308db3-8c21-4eba-bd28-4114843e291b"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
